--- a/output/pdf_financials_xlsx/XLY.xlsx
+++ b/output/pdf_financials_xlsx/XLY.xlsx
@@ -6094,31 +6094,31 @@
         <v>0.190041</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>18.206</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>55.567</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>89.84399999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>98.047</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>110.958</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>114.947</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>117.563</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>102.844</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>116.318</v>
       </c>
     </row>
     <row r="93">
@@ -12032,7 +12032,11 @@
           <t>Reserves (Note 16)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -14744,7 +14748,11 @@
           <t>Reserves (Note 17)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -16614,7 +16622,11 @@
           <t>Reserves (Note 18)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -18832,7 +18844,11 @@
           <t>Reserves (Note 20)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -22498,7 +22514,11 @@
           <t>Reserves (Note 15)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XLY.xlsx
+++ b/output/pdf_financials_xlsx/XLY.xlsx
@@ -961,34 +961,34 @@
         <v>0.216387</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.081113</v>
+        <v>0.587923</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.553612</v>
+        <v>20.394</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>48.373</v>
+        <v>61.909</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>50.291</v>
+        <v>70.986</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>46.629</v>
+        <v>68.59399999999999</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>44.288</v>
+        <v>75.896</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>46.649</v>
+        <v>87.066</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>38.641</v>
+        <v>72.94</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>35.676</v>
+        <v>60.256</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>43.352</v>
+        <v>60.73</v>
       </c>
     </row>
     <row r="11">
@@ -1025,31 +1025,31 @@
         <v>-0.359406</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.175626</v>
+        <v>-19.016014</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-47.626</v>
+        <v>-61.162</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-41.939</v>
+        <v>-62.634</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-36.817</v>
+        <v>-58.782</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-24.998</v>
+        <v>-56.606</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-30.137</v>
+        <v>-70.554</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-17.364</v>
+        <v>-51.663</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>24.253</v>
+        <v>-0.327</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>43.392</v>
+        <v>26.014</v>
       </c>
     </row>
     <row r="12">
@@ -1086,13 +1086,13 @@
         <v>0.002716</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>3.612</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -2085,13 +2085,13 @@
         <v>-0.278293</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-18.177</v>
+        <v>-18.344</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-67.209</v>
+        <v>-71.209</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-108.618</v>
+        <v>-112.23</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-86.575</v>
@@ -2207,13 +2207,13 @@
         <v>-0.278293</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-18.145</v>
+        <v>-18.312</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-65.146</v>
+        <v>-69.146</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-100.044</v>
+        <v>-103.656</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-77.59399999999999</v>
@@ -2278,13 +2278,13 @@
         <v>-120.3517664001245</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1316.776803247638</v>
+        <v>-1328.89593943625</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-8721.017402945114</v>
+        <v>-9256.492637215528</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-1197.844827586207</v>
+        <v>-1241.091954022989</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-790.8071748878924</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.104413</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.173396</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.173396</v>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.104413</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.173396</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.173396</v>
@@ -3305,10 +3305,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.158204</v>
+        <v>0.053791</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.179696</v>
+        <v>0.0063</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -26278,7 +26278,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -63494,7 +63494,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -69848,7 +69848,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -72488,7 +72488,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -72700,7 +72700,7 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
@@ -75438,7 +75438,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -76504,7 +76504,7 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -77142,7 +77142,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -82308,7 +82308,7 @@
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">

--- a/output/pdf_financials_xlsx/XLY.xlsx
+++ b/output/pdf_financials_xlsx/XLY.xlsx
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.022619</v>
+        <v>0.067979</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.075881</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.022619</v>
+        <v>0.067979</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.244441</v>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.008014</v>
+        <v>0.008014</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0.038</v>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>0.034444</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0.06908499999999999</v>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0</v>
+        <v>0.034444</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0.072085</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.053791</v>
+        <v>0.019347</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.0063</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0</v>
+        <v>0.018887</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0.018887</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>1.758106</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>1.758106</v>
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.143191</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.186059</v>
@@ -27568,7 +27568,11 @@
           <t>Accounts receivable – Note 7</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="n">
         <v>0.034444</v>
       </c>
@@ -27672,7 +27676,11 @@
           <t>Due from related parties – Note 7</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -27778,7 +27786,11 @@
           <t>Equipment – Note 5</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -27988,7 +28000,11 @@
           <t>Investment – Note 4</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E186" s="5" t="n">
         <v>0.018887</v>
       </c>
@@ -28092,7 +28108,11 @@
           <t>Income taxes payable – Note 8</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>IncomeTaxPayable</t>
+        </is>
+      </c>
       <c r="E187" s="5" t="n">
         <v>0.008014</v>
       </c>
@@ -28196,7 +28216,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E188" s="5" t="n">
         <v>1.758106</v>
       </c>
@@ -28300,7 +28324,11 @@
           <t>Contributed surplus – Note 6</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E189" s="5" t="n">
         <v>0.143191</v>
       </c>
@@ -89660,7 +89688,11 @@
           <t>Administration fees – Note 7</t>
         </is>
       </c>
-      <c r="D774" t="inlineStr"/>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E774" s="5" t="n">
         <v>0.04536</v>
       </c>
@@ -89972,7 +90004,11 @@
           <t>Management fees – Note 7</t>
         </is>
       </c>
-      <c r="D777" t="inlineStr"/>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E777" t="inlineStr">
         <is>
           <t>-</t>
@@ -90712,7 +90748,11 @@
           <t>Provision for current income taxes – Note 8</t>
         </is>
       </c>
-      <c r="D784" t="inlineStr"/>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E784" s="5" t="n">
         <v>-0.008014</v>
       </c>

--- a/output/pdf_financials_xlsx/XLY.xlsx
+++ b/output/pdf_financials_xlsx/XLY.xlsx
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.067979</v>
+        <v>0.133979</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.075881</v>
+        <v>0.118081</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.336526</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.231233</v>
+        <v>0.260983</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>16.144</v>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.067979</v>
+        <v>0.133979</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.244441</v>
@@ -1330,13 +1330,13 @@
         <v>-0.275577</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-18.177</v>
+        <v>-17.505</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-67.209</v>
+        <v>-64.896</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-108.618</v>
+        <v>-97.64</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-86.575</v>
@@ -1388,34 +1388,34 @@
         <v>-0.011636</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.046</v>
+        <v>-0.046</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.672</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.313</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-10.978</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0.856</v>
+        <v>-0.681</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>16.486</v>
+        <v>-4.33</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6.262</v>
+        <v>-6.262</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>3.238</v>
+        <v>-3.238</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-15.992</v>
+        <v>15.992</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>9.337999999999999</v>
+        <v>-9.337999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>-1.537</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>12.156</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -2085,13 +2085,13 @@
         <v>-0.278293</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-18.344</v>
+        <v>-17.672</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-71.209</v>
+        <v>-68.896</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-112.23</v>
+        <v>-101.252</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-86.575</v>
@@ -2207,13 +2207,13 @@
         <v>-0.278293</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-18.312</v>
+        <v>-17.64</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-69.146</v>
+        <v>-66.833</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-103.656</v>
+        <v>-92.678</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-77.59399999999999</v>
@@ -2278,13 +2278,13 @@
         <v>-120.3517664001245</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1328.89593943625</v>
+        <v>-1280.129115970699</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-9256.492637215528</v>
+        <v>-8946.854082998661</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-1241.091954022989</v>
+        <v>-1109.650383141762</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-790.8071748878924</v>
@@ -2339,19 +2339,19 @@
         <v>-16.69224935317534</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.838903170522708</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.564164201183432</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.24334289225727</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.9887380883626913</v>
+        <v>-0.7866012128212533</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-32.81449044585987</v>
+        <v>-8.618630573248408</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-4.585698070374574</v>
@@ -7142,10 +7142,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>1.487</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>4.642</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -7157,10 +7157,10 @@
         <v>0</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>14.867</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>16.345</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>0</v>
@@ -7179,10 +7179,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001017</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>0.000763</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7444,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>-0.081113</v>
+        <v>0.1</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -7508,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-11.088</v>
       </c>
       <c r="L116" s="3" t="n">
         <v>0</v>
@@ -8636,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001017</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000763</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -32546,7 +32546,11 @@
           <t>Interest and accretion expense (Note 23)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -48550,7 +48554,11 @@
           <t>Accretion expense (Note 13)</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -48864,7 +48872,11 @@
           <t>Deferred income tax recovery (Note 20)</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -52036,7 +52048,11 @@
           <t>Accretion expense (Note 10, 11)</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -52248,7 +52264,11 @@
           <t>Deferred income tax expense (recovery) (Note 17)</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -53096,7 +53116,11 @@
           <t>Purchase of intangible assets (Note 6)</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -53202,7 +53226,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -56492,7 +56520,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -60410,7 +60442,11 @@
           <t>Disposition (Purchase) of equipment</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -61684,7 +61720,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -64236,7 +64276,11 @@
           <t>Income tax recovery/(expense) (Notes 9, 13, 24)</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -65484,7 +65528,11 @@
           <t>Income tax recovery/(expense) (Note 24)</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -66940,7 +66988,11 @@
           <t>Income tax recovery/(expense) (Note 25)</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -68406,7 +68458,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -70604,7 +70656,11 @@
           <t>Income tax recovery (Note 27)</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>-</t>
@@ -70710,7 +70766,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -73568,7 +73624,11 @@
           <t>Income tax recovery (Note 25)</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E621" t="inlineStr">
         <is>
           <t>-</t>
@@ -77380,7 +77440,11 @@
           <t>Income tax recovery (Note 20)</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E657" t="inlineStr">
         <is>
           <t>-</t>
@@ -81696,7 +81760,11 @@
           <t>Director fees (Note 13)</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E698" t="inlineStr">
         <is>
           <t>-</t>
@@ -83066,7 +83134,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D711" t="inlineStr"/>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E711" t="inlineStr">
         <is>
           <t>-</t>
@@ -87678,7 +87750,11 @@
           <t>Directors’ fees (note 6)</t>
         </is>
       </c>
-      <c r="D755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E755" t="inlineStr">
         <is>
           <t>-</t>
@@ -89796,7 +89872,11 @@
           <t>Directors’ fees – Note 7</t>
         </is>
       </c>
-      <c r="D775" t="inlineStr"/>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E775" s="5" t="n">
         <v>0.066</v>
       </c>
